--- a/pipeline/credit_rating/output/equity_xhtn_20260923.xlsx
+++ b/pipeline/credit_rating/output/equity_xhtn_20260923.xlsx
@@ -5036,7 +5036,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>14/12/2025</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
